--- a/src/election.xlsx
+++ b/src/election.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darsh\IdeaProjects\Computer Project\src\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -58,6 +58,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -396,34 +397,34 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>0</v>
       </c>
     </row>
@@ -433,34 +434,34 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>0</v>
       </c>
     </row>
@@ -470,34 +471,34 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0">
         <v>0</v>
       </c>
     </row>
@@ -507,34 +508,34 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="0">
         <v>0</v>
       </c>
     </row>
